--- a/5_First_clinical_assessment.xlsx
+++ b/5_First_clinical_assessment.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D4YKH4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wrk\phd\HIS_Forms_for_Stroke_Care\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB382201-BEC5-42EE-9A66-B58B0EBCA14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316A5C5D-D8A9-48FC-857B-CCD66338D67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -316,9 +316,6 @@
     <t>Other hemorrhagic complication</t>
   </si>
   <si>
-    <t>Reason for withholding recanalization therapy</t>
-  </si>
-  <si>
     <t>Arrived outside the therapeutic time window</t>
   </si>
   <si>
@@ -341,6 +338,9 @@
   </si>
   <si>
     <t>IF Reason for withholding recanalization = Other</t>
+  </si>
+  <si>
+    <t>Reason for withholding thrombolysis</t>
   </si>
 </sst>
 </file>
@@ -591,37 +591,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -955,19 +955,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -979,13 +979,13 @@
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -998,8 +998,8 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="25"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="35"/>
       <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
@@ -1010,16 +1010,16 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="25"/>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="27" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="6"/>
@@ -1028,28 +1028,28 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="25"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="27"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="24"/>
+      <c r="E5" s="26"/>
       <c r="F5" s="6"/>
       <c r="G5" s="7"/>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="25"/>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="27" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="6"/>
@@ -1058,28 +1058,28 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="25"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="6"/>
       <c r="G7" s="10"/>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" s="25"/>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="27" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="6"/>
@@ -1088,28 +1088,28 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="25"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="24"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="6"/>
       <c r="G9" s="10"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" s="25"/>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="27" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="6"/>
@@ -1130,28 +1130,28 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="26"/>
       <c r="F12" s="6"/>
       <c r="G12" s="10"/>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="27" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="6"/>
@@ -1172,28 +1172,28 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="25"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="24"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="6"/>
       <c r="G15" s="10"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="27" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="6"/>
@@ -1202,18 +1202,18 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
       <c r="D17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="24"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="6"/>
       <c r="G17" s="10"/>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="24"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="6" t="s">
         <v>28</v>
       </c>
@@ -1233,13 +1233,13 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -1254,8 +1254,8 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
       <c r="D20" s="6" t="s">
         <v>36</v>
       </c>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="27" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -1284,7 +1284,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="25"/>
-      <c r="B22" s="24"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="8" t="s">
         <v>40</v>
       </c>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="25"/>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="27" t="s">
         <v>41</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -1313,8 +1313,8 @@
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
       <c r="C24" s="8" t="s">
         <v>40</v>
       </c>
@@ -1327,7 +1327,7 @@
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="27" t="s">
         <v>43</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -1342,7 +1342,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="25"/>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="27" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -1355,8 +1355,8 @@
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="8" t="s">
         <v>40</v>
       </c>
@@ -1367,7 +1367,7 @@
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="27" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="13"/>
@@ -1379,7 +1379,7 @@
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="24"/>
+      <c r="A29" s="26"/>
       <c r="B29" s="16" t="s">
         <v>47</v>
       </c>
@@ -1397,13 +1397,13 @@
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="29" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="17" t="s">
@@ -1525,7 +1525,7 @@
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" s="25"/>
       <c r="B40" s="25"/>
-      <c r="C40" s="24"/>
+      <c r="C40" s="26"/>
       <c r="D40" s="15" t="s">
         <v>63</v>
       </c>
@@ -1535,7 +1535,7 @@
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="24"/>
+      <c r="A41" s="26"/>
       <c r="B41" s="20" t="s">
         <v>64</v>
       </c>
@@ -1554,17 +1554,17 @@
       <c r="A42" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="29" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E42" s="12"/>
-      <c r="F42" s="33" t="s">
+      <c r="F42" s="24" t="s">
         <v>30</v>
       </c>
       <c r="G42" s="10" t="s">
@@ -1629,14 +1629,14 @@
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
       <c r="D47" s="21" t="s">
         <v>74</v>
       </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="24"/>
+      <c r="F47" s="26"/>
       <c r="G47" s="10" t="s">
         <v>69</v>
       </c>
@@ -1661,19 +1661,19 @@
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="E49" s="27" t="s">
         <v>35</v>
       </c>
       <c r="F49" s="6"/>
@@ -1681,19 +1681,19 @@
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A50" s="30"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
+      <c r="A50" s="31"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
       <c r="D50" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E50" s="24"/>
+      <c r="E50" s="26"/>
       <c r="F50" s="12"/>
       <c r="G50" s="10"/>
       <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="12" t="s">
         <v>82</v>
       </c>
@@ -1709,7 +1709,7 @@
       <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="12" t="s">
         <v>85</v>
       </c>
@@ -1725,7 +1725,7 @@
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="21" t="s">
         <v>86</v>
       </c>
@@ -1741,7 +1741,7 @@
       <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="21" t="s">
         <v>88</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>89</v>
       </c>
       <c r="D54" s="12"/>
-      <c r="E54" s="23" t="s">
+      <c r="E54" s="27" t="s">
         <v>84</v>
       </c>
       <c r="F54" s="12" t="s">
@@ -1761,11 +1761,11 @@
       <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A55" s="30"/>
-      <c r="B55" s="23" t="s">
+      <c r="A55" s="31"/>
+      <c r="B55" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="6" t="s">
@@ -1777,29 +1777,29 @@
       <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A56" s="30"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
+      <c r="A56" s="31"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
       <c r="D56" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E56" s="24"/>
+      <c r="E56" s="26"/>
       <c r="F56" s="12"/>
       <c r="G56" s="10"/>
       <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A57" s="30"/>
-      <c r="B57" s="23" t="s">
+      <c r="A57" s="31"/>
+      <c r="B57" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="27" t="s">
         <v>94</v>
       </c>
       <c r="D57" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E57" s="23" t="s">
+      <c r="E57" s="27" t="s">
         <v>84</v>
       </c>
       <c r="F57" s="12"/>
@@ -1807,7 +1807,7 @@
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A58" s="30"/>
+      <c r="A58" s="31"/>
       <c r="B58" s="25"/>
       <c r="C58" s="25"/>
       <c r="D58" s="12" t="s">
@@ -1819,41 +1819,41 @@
       <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A59" s="30"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
+      <c r="A59" s="31"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
       <c r="D59" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E59" s="24"/>
+      <c r="E59" s="26"/>
       <c r="F59" s="12"/>
       <c r="G59" s="10"/>
       <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A60" s="30"/>
-      <c r="B60" s="23" t="s">
+      <c r="A60" s="31"/>
+      <c r="B60" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C60" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D60" s="22" t="s">
+      <c r="E60" s="27" t="s">
         <v>99</v>
-      </c>
-      <c r="E60" s="23" t="s">
-        <v>100</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="10"/>
       <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
       <c r="D61" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E61" s="25"/>
       <c r="F61" s="12"/>
@@ -1861,11 +1861,11 @@
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="25"/>
       <c r="C62" s="25"/>
       <c r="D62" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E62" s="25"/>
       <c r="F62" s="12"/>
@@ -1873,11 +1873,11 @@
       <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
       <c r="D63" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E63" s="25"/>
       <c r="F63" s="12"/>
@@ -1885,11 +1885,11 @@
       <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="25"/>
       <c r="C64" s="25"/>
       <c r="D64" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E64" s="25"/>
       <c r="F64" s="12"/>
@@ -1897,11 +1897,11 @@
       <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
       <c r="D65" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E65" s="25"/>
       <c r="F65" s="12"/>
@@ -1909,19 +1909,19 @@
       <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A66" s="30"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
+      <c r="A66" s="31"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
       <c r="D66" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E66" s="24"/>
+      <c r="E66" s="26"/>
       <c r="F66" s="12"/>
       <c r="G66" s="10"/>
       <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12" t="s">
         <v>65</v>
@@ -1930,7 +1930,7 @@
         <v>63</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
@@ -1938,6 +1938,39 @@
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="B60:B66"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E60:E66"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A49:A67"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C42:C47"/>
+    <mergeCell ref="C60:C66"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="B42:B47"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B21:B22"/>
     <mergeCell ref="F42:F47"/>
     <mergeCell ref="A30:A41"/>
     <mergeCell ref="B19:B20"/>
@@ -1954,39 +1987,6 @@
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="C30:C40"/>
     <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A49:A67"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C42:C47"/>
-    <mergeCell ref="C60:C66"/>
-    <mergeCell ref="A43:A47"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B60:B66"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E60:E66"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
